--- a/test-cases/e2e-test-cases.xlsx
+++ b/test-cases/e2e-test-cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17580" activeTab="1"/>
+    <workbookView windowWidth="25800" windowHeight="17580"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="2" r:id="rId1"/>
@@ -60,7 +60,7 @@
     <t>Verify End-to-End Purchase Flow with Two Products</t>
   </si>
   <si>
-    <t>End-to-End Testing</t>
+    <t>Positive</t>
   </si>
   <si>
     <t>1. ผู้ใช้ยังไม่ได้เข้าสู่ระบบและอยู่ที่หน้า Login
@@ -80,7 +80,7 @@
 3. คลิก Login
 4. เลือกสินค้า Sauce Labs Backpack และ Sauce Labs Bike Light 
 5. คลิกปุ่ม Add to Cart สินค้าทั้ง 2 รายการ
-6. หลังเปิด Cart ให้เพิ่มการตรวจสอบชื่อและจำนวนสินค้าทั้ง 2 รายการ ก่อนคลิก Checkout เพื่อยืนยันข้อมูลระหว่างขั้นตอน
+6. หลังเปิด Shopping Cart ตรวจสอบชื่อและจำนวนสินค้าทั้ง 2 รายการ ก่อนคลิก Checkout
 7. ในหน้า Your Information กรอก 
 -First Name: John
 -Last Name: Doe
@@ -1351,6 +1351,7 @@
     <col min="5" max="5" width="63.375" customWidth="1"/>
     <col min="6" max="6" width="74.25" customWidth="1"/>
     <col min="7" max="7" width="59.625" customWidth="1"/>
+    <col min="8" max="8" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:8">
@@ -1386,7 +1387,7 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">

--- a/test-cases/e2e-test-cases.xlsx
+++ b/test-cases/e2e-test-cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17580" activeTab="2"/>
+    <workbookView windowHeight="17580"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="77">
   <si>
     <t>SAUCEDEMO  /  END-TO-END</t>
   </si>
@@ -40,7 +40,7 @@
     <t>PORTFOLIO  •  SOURCE: SAUCEDEMO</t>
   </si>
   <si>
-    <t>1 TEST CASES   •   1 PASS</t>
+    <t>1 TEST CASE   •   1 PASS</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -193,12 +193,41 @@
     <t>Verify the completed order and confirmation message.</t>
   </si>
   <si>
-    <t>The Order Complete page appears and displays "Thank you for your order!".</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The Order Complete page appears and displays "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Thank you for your order!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
   </si>
   <si>
     <t>MANUAL QA TEST DOCUMENTATION   •   TEST EXECUTION RESULTS</t>
   </si>
   <si>
+    <t>Evidence screenshots are grouped by Test Case ID, not individually mapped to each Actual Result entry. One screenshot may support multiple observations.</t>
+  </si>
+  <si>
     <t>Actual Result</t>
   </si>
   <si>
@@ -217,24 +246,72 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>1. Login succeeded, and the Products page opened.
-2. Backpack and Bike Light were added to the cart, quantity 1 each.
-3. The cart badge displayed 2, and both items appeared in the Shopping Cart.
-4. After entering purchaser information, the application navigated to Checkout Overview.
-5. Product names, quantities, and prices matched: Backpack $29.99; Bike Light $9.99.
-6. Item Total was $39.98; Tax was $3.20; Total was $43.18.
-7. After clicking Finish, the Order Complete page displayed "Thank you for your order!".</t>
+    <t>1. Login succeeded, and the Products page opened.</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_LOGIN.png
-2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_PRODUCTS.png
-3. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_CART.png
-4. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_INFORMATION.png
-5. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_OVERVIEW.png
-6. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_COMPLETE.png</t>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_LOGIN.png</t>
+  </si>
+  <si>
+    <t>2. Backpack and Bike Light were added to the cart, quantity 1 each.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_PRODUCTS.png</t>
+  </si>
+  <si>
+    <t>3. The cart badge displayed 2, and both items appeared in the Shopping Cart.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_CART.png</t>
+  </si>
+  <si>
+    <t>4. After entering purchaser information, the application navigated to Checkout Overview.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_INFORMATION.png</t>
+  </si>
+  <si>
+    <t>5. Product names, quantities, and prices matched: Backpack $29.99; Bike Light $9.99.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_OVERVIEW.png</t>
+  </si>
+  <si>
+    <t>6. Item Total was $39.98; Tax was $3.20; Total was $43.18.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_COMPLETE.png</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7. After clicking Finish, the Order Complete page displayed "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Thank you for your order!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>".</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -248,7 +325,7 @@
     <numFmt numFmtId="179" formatCode="_-&quot;฿&quot;* #,##0_-;\-&quot;฿&quot;* #,##0_-;_-&quot;฿&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -276,6 +353,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF002060"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color theme="3" tint="0.1"/>
@@ -296,6 +379,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="3" tint="0.1"/>
       <name val="Aptos"/>
@@ -304,12 +393,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -424,8 +507,14 @@
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -464,12 +553,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7FAFD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -655,7 +738,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -722,6 +805,56 @@
       <top style="hair">
         <color auto="1"/>
       </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="hair">
         <color auto="1"/>
       </bottom>
@@ -874,152 +1007,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1042,78 +1175,106 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1171,7 +1332,17 @@
   <dxfs count="22">
     <dxf>
       <font>
-        <color theme="9"/>
+        <color theme="5"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
@@ -1181,17 +1352,7 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0070C0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="5"/>
+        <color theme="9"/>
       </font>
     </dxf>
     <dxf>
@@ -1408,6 +1569,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="12"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="00E9F1F9"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1623,44 +1789,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:7">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="18"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:7">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="21"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="28"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:7">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="24" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="31"/>
     </row>
     <row r="4" ht="11" customHeight="1" spans="1:7">
-      <c r="A4" s="26"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="28"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="34"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:7">
       <c r="A5" s="10" t="s">
@@ -1681,30 +1847,30 @@
       <c r="F5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="G5" s="39" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" ht="50" customHeight="1" spans="1:7">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="43" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1739,40 +1905,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:5">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="18"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="21"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="28"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:5">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="24" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
     </row>
     <row r="4" ht="11" customHeight="1" spans="1:5">
-      <c r="A4" s="26"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5">
       <c r="A5" s="10" t="s">
@@ -1792,214 +1958,214 @@
       </c>
     </row>
     <row r="6" ht="29" customHeight="1" spans="1:5">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="36">
         <v>1</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="37" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" ht="29" customHeight="1" spans="1:5">
-      <c r="A7" s="32"/>
-      <c r="B7" s="30">
+      <c r="A7" s="38"/>
+      <c r="B7" s="36">
         <v>2</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="37" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8" ht="29" customHeight="1" spans="1:5">
-      <c r="A8" s="32"/>
-      <c r="B8" s="30">
+      <c r="A8" s="38"/>
+      <c r="B8" s="36">
         <v>3</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="37" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" ht="29" customHeight="1" spans="1:5">
-      <c r="A9" s="32"/>
-      <c r="B9" s="30">
+      <c r="A9" s="38"/>
+      <c r="B9" s="36">
         <v>4</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="37" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" ht="29" customHeight="1" spans="1:5">
-      <c r="A10" s="32"/>
-      <c r="B10" s="30">
+      <c r="A10" s="38"/>
+      <c r="B10" s="36">
         <v>5</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="37" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" ht="29" customHeight="1" spans="1:5">
-      <c r="A11" s="32"/>
-      <c r="B11" s="30">
+      <c r="A11" s="38"/>
+      <c r="B11" s="36">
         <v>6</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="37" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" ht="29" customHeight="1" spans="1:5">
-      <c r="A12" s="32"/>
-      <c r="B12" s="30">
+      <c r="A12" s="38"/>
+      <c r="B12" s="36">
         <v>7</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="37" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" ht="29" customHeight="1" spans="1:5">
-      <c r="A13" s="32"/>
-      <c r="B13" s="30">
+      <c r="A13" s="38"/>
+      <c r="B13" s="36">
         <v>8</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="37" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5">
-      <c r="A14" s="32"/>
-      <c r="B14" s="30">
+      <c r="A14" s="38"/>
+      <c r="B14" s="36">
         <v>9</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="37" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5">
-      <c r="A15" s="32"/>
-      <c r="B15" s="30">
+      <c r="A15" s="38"/>
+      <c r="B15" s="36">
         <v>10</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="37" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" ht="29" customHeight="1" spans="1:5">
-      <c r="A16" s="32"/>
-      <c r="B16" s="30">
+      <c r="A16" s="38"/>
+      <c r="B16" s="36">
         <v>11</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="37" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" ht="29" customHeight="1" spans="1:5">
-      <c r="A17" s="32"/>
-      <c r="B17" s="30">
+      <c r="A17" s="38"/>
+      <c r="B17" s="36">
         <v>12</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="37" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="18" ht="29" customHeight="1" spans="1:5">
-      <c r="A18" s="32"/>
-      <c r="B18" s="30">
+      <c r="A18" s="38"/>
+      <c r="B18" s="36">
         <v>13</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="37" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1" spans="1:5">
-      <c r="A19" s="32"/>
-      <c r="B19" s="30">
+      <c r="A19" s="38"/>
+      <c r="B19" s="36">
         <v>14</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="37" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2019,13 +2185,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="67.25" customWidth="1"/>
+    <col min="4" max="4" width="93.75" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="52" customWidth="1"/>
@@ -2067,8 +2233,10 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
     </row>
-    <row r="4" ht="11" customHeight="1" spans="1:7">
-      <c r="A4" s="8"/>
+    <row r="4" customFormat="1" ht="23" customHeight="1" spans="1:7">
+      <c r="A4" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -2081,65 +2249,148 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" ht="255" customHeight="1" spans="1:7">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1" spans="1:7">
       <c r="A6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15">
+      <c r="D6" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16">
         <v>46309</v>
       </c>
-      <c r="G6" s="14"/>
+      <c r="G6" s="15"/>
+    </row>
+    <row r="7" ht="41" customHeight="1" spans="1:7">
+      <c r="A7" s="17"/>
+      <c r="B7" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="20"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:7">
+      <c r="A8" s="17"/>
+      <c r="B8" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="20"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" ht="44" customHeight="1" spans="1:7">
+      <c r="A9" s="17"/>
+      <c r="B9" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="18"/>
+      <c r="D9" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:7">
+      <c r="A10" s="17"/>
+      <c r="B10" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="20"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" ht="37" customHeight="1" spans="1:7">
+      <c r="A11" s="17"/>
+      <c r="B11" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" ht="45" customHeight="1" spans="1:7">
+      <c r="A12" s="22"/>
+      <c r="B12" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="23"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="11">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="D3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A6:A12"/>
+    <mergeCell ref="C6:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E6:E12"/>
+    <mergeCell ref="F6:F12"/>
+    <mergeCell ref="G6:G12"/>
   </mergeCells>
   <conditionalFormatting sqref="C6">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
-      <formula>"PASS"</formula>
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"NEEDS CLARIFICATION"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
-      <formula>"FAIL"</formula>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"NOT RUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"BLOCKED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>"NOT RUN"</formula>
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+      <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
-      <formula>"NEEDS CLARIFICATION"</formula>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+      <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -2147,6 +2398,14 @@
       <formula1>"PASS,FAIL,BLOCKED,NOT RUN,NEEDS CLARIFICATION"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="D6" r:id="rId1" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_LOGIN.png"/>
+    <hyperlink ref="D7" r:id="rId2" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_PRODUCTS.png"/>
+    <hyperlink ref="D8" r:id="rId3" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_CART.png"/>
+    <hyperlink ref="D9" r:id="rId4" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_INFORMATION.png"/>
+    <hyperlink ref="D10" r:id="rId5" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_OVERVIEW.png"/>
+    <hyperlink ref="D11" r:id="rId6" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/e2e/TC-E2E-001_COMPLETE.png"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
